--- a/ig/DM-37/ValueSet-JDV-J70-Equipement-Santefr.xlsx
+++ b/ig/DM-37/ValueSet-JDV-J70-Equipement-Santefr.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="295">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-26T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -318,13 +318,13 @@
     <t>098</t>
   </si>
   <si>
-    <t>Bassin thérapeutique pour balnéothérapie (&lt;20m2)</t>
+    <t>Bassin thérapeutique pour balnéothérapie (&lt;25m2)</t>
   </si>
   <si>
     <t>099</t>
   </si>
   <si>
-    <t>Piscine pour balnéothérapie (&gt;20m2)</t>
+    <t>Bassin thérapeutique pour balnéothérapie (&gt;=25m2)</t>
   </si>
   <si>
     <t>100</t>
@@ -877,6 +877,18 @@
   </si>
   <si>
     <t>Arthromoteurs membres supérieurs (épaules, coudes)</t>
+  </si>
+  <si>
+    <t>211</t>
+  </si>
+  <si>
+    <t>Salle hybride</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>Vidéo assistance</t>
   </si>
   <si>
     <t/>
@@ -1155,7 +1167,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B132"/>
+  <dimension ref="A1:B134"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2207,15 +2219,31 @@
         <v>288</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>294</v>
       </c>
     </row>
   </sheetData>
